--- a/output/pdf_financials_xlsx/ALFA.UN.xlsx
+++ b/output/pdf_financials_xlsx/ALFA.UN.xlsx
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>6.2e-05</v>
       </c>
     </row>
     <row r="35">
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>6.2e-05</v>
       </c>
     </row>
     <row r="37">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">

--- a/output/pdf_financials_xlsx/ALFA.UN.xlsx
+++ b/output/pdf_financials_xlsx/ALFA.UN.xlsx
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.000425</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.000156</v>
       </c>
     </row>
     <row r="101">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">

--- a/output/pdf_financials_xlsx/ALFA.UN.xlsx
+++ b/output/pdf_financials_xlsx/ALFA.UN.xlsx
@@ -1998,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>0.00063</v>
       </c>
     </row>
     <row r="117">
@@ -3348,7 +3348,11 @@
           <t>Acquisition of intangible assets (1</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
